--- a/training/triathlon_plan.xlsx
+++ b/training/triathlon_plan.xlsx
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F4B942"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4B942"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -683,9 +683,9 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>W1 平稳重启
+          <t>W1 直接开干
 2026-03-23～2026-03-29
-📌 从低负荷状态平稳过渡，游泳建立结构化组次，骑行控制心率重建有氧基础</t>
+📌 已有3月基础，W1直接上强度。节奏跑+阈值段落，游泳结构化，周末Brick骑行提心率至Z3</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -710,17 +710,17 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 5km</t>
+          <t>节奏跑 6km（热身1km+节奏4km @6:20-6:40/km+放松1km）</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Z2 (111-130bpm)</t>
+          <t>Z2-Z3</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>跑步机或户外，保持对话配速</t>
+          <t>心率目标Z3(130-148)，乳酸阈值下方</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>3×250m（组间休息30s，专注划水节奏）</t>
+          <t>4×200m（组间30s）+ 200m计时（记录成绩）</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Z2</t>
+          <t>Z2-Z3</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>25m泳池，感受水感</t>
+          <t>200m目标&lt;6min，感受配速</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 5km + 末段4×100m提速</t>
+          <t>阈值间歇：3×1km @Z4（148-167bpm），组间慢跑90s</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Z2末段Z3</t>
+          <t>Z4</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>跑完拉伸10min</t>
+          <t>配速目标5:45-6:10/km，比乳酸阈值配速稍慢</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 5km</t>
+          <t>轻松跑 6km（Z2，主动恢复）</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -870,7 +870,11 @@
           <t>Z2</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>比昨天间歇后的恢复跑，保持轻松</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="6" t="n"/>
@@ -886,7 +890,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>🚴 BIKE</t>
+          <t>🧱 BRICK</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -896,17 +900,17 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>骑行 25km（踏频85rpm，稳定有氧）</t>
+          <t>🧱砖训：骑30km（HR 140-155，Z3-Z4）→ 立即跑5km（目标6:40-7:00）</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Z2 (111-130bpm)</t>
+          <t>骑Z3-Z4/跑Z3</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>户外，专注踏频不是速度</t>
+          <t>骑行HR要比3/22的129高！感受比赛强度</t>
         </is>
       </c>
     </row>
@@ -934,26 +938,26 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>4×150m（感受配速，组间20s）</t>
+          <t>🎯750m基准计时（连续，全程记录时间）</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Z2</t>
+          <t>Z3</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>记录每组时间</t>
+          <t>建立基准，后续各周对比进步</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>W2 负荷上升
+          <t>W2 强度巩固
 2026-03-30～2026-04-05
-📌 引入节奏跑，骑行距离提升至30km，加入骑跑砖训</t>
+📌 跑步加入长距节奏跑，游泳超距800m，骑行Brick提速</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -978,17 +982,17 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>节奏跑 5km（含中间3km @ Z3配速约6:30-6:45）</t>
+          <t>长跑 8km（全程Z2，稳定7:00-7:30配速）</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Z2-Z3</t>
+          <t>Z2</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>热身1km+节奏3km+放松1km</t>
+          <t>有氧基础，别追配速，保持心率Z2</t>
         </is>
       </c>
     </row>
@@ -1016,15 +1020,19 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>4×200m（组间30s，专注换气节奏）</t>
+          <t>2×400m（Z3）+ 100m放松</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr"/>
+          <t>Z3+Z2</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>400m目标&lt;12min</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="6" t="n"/>
@@ -1050,12 +1058,12 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 6km</t>
+          <t>节奏跑 6km（热身1km+节奏4km @6:20-6:40+放松1km）</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Z2</t>
+          <t>Z2-Z3</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
@@ -1118,51 +1126,55 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 5km</t>
+          <t>阈值间歇：4×1km @Z4，组间慢跑90s</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
+          <t>Z4</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>比W1多一组，配速目标5:45-6:10</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="6" t="n"/>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>04/04</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>🧱 BRICK</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>周末全天</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>🧱砖训：骑30km（HR 135-148）→ 立即跑3km</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>骑Z3/跑Z2-Z3</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>骑完不休息直接换跑鞋出发</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>🧱砖训：骑35km（HR 143-155，Z3-Z4）→ 立即跑5km（目标6:30-6:45）</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>骑Z3-Z4/跑Z3</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>骑行距离提升5km，跑步配速提升</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1202,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>600m连续游（基准测试，记录全程时间）</t>
+          <t>超距：800m连续游</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -1200,16 +1212,16 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>目标&lt;18min，记录成绩</t>
+          <t>不停顿，对比750m基准感受余量</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>W3 专项强化
+          <t>W3 骑行强化
 2026-04-06～2026-04-12
-📌 骑行强度提升（含Z3区间段），跑步引入乳酸阈值训练，游泳超距</t>
+📌 骑行强度最强周（含高强度区间），跑步维持阈值，游泳1000m超距</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1234,15 +1246,19 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 6km</t>
+          <t>节奏跑 6km（热身1km+节奏4km @6:10-6:30+放松1km）</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>Z3</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>比W2配速再提5-10s</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="6" t="n"/>
@@ -1268,17 +1284,17 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>2×400m（Z3强度）+ 200m放松</t>
+          <t>超距：1000m连续游</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Z3+Z2</t>
+          <t>Z2-Z3</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>400m目标约12min</t>
+          <t>目标&lt;31min，建立信心</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1322,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>阈值跑：4×1km @ Z4（148-167bpm），组间慢跑2min</t>
+          <t>阈值间歇：5×1km @Z4，组间慢跑90s</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1316,7 +1332,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>配速目标5:45-6:10/km</t>
+          <t>本周最高强度跑，配速5:40-6:05</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1394,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 6km</t>
+          <t>轻松跑 6km（Z2，恢复）</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1390,39 +1406,39 @@
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="6" t="n"/>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>04/11</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>🚴 BIKE</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>周末全天</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>骑行 35km（含15km @ Z3区间，HR 130-148）</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>Z2-Z3</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>前10km热身，中15km提速，末10km有氧</t>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>骑行 40km（含20km @ Z3-Z4，HR 143-160）</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Z2-Z4</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>前10km热身，中20km强度，末10km Z2收尾</t>
         </is>
       </c>
     </row>
@@ -1450,26 +1466,22 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>超距：800m连续游</t>
+          <t>4×200m（Z3）+ 200m放松</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Z2-Z3</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>不停顿，感受750m+余量</t>
-        </is>
-      </c>
+          <t>Z3</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>W4 整合测试
 2026-04-13～2026-04-19
-📌 750m游泳基准计时测试，骑行砖训提升强度，跑步配速推进</t>
+📌 750m游泳计时测试（对比W1基准），完整Brick升级为骑跑全距，跑步配速推进</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1494,7 +1506,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>节奏跑 6km（含4km @ Z3，配速6:20-6:40）</t>
+          <t>节奏跑 7km（热身1km+节奏5km @6:10-6:30+放松1km）</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1528,7 +1540,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>🎯750m基准计时（全力连续，记录成绩）</t>
+          <t>🎯750m计时测试（对比W1成绩）</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1538,7 +1550,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>目标&lt;23min，记录用于追踪进步</t>
+          <t>记录成绩，应比W1快</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1578,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 6km</t>
+          <t>轻松跑 6km（Z2，游泳测试后恢复）</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1650,37 +1662,37 @@
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="6" t="n"/>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>04/18</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>🧱 BRICK</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>周末全天</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>🧱砖训：骑30km（HR 143-155，Z3-Z4）→ 跑5km（目标6:30-6:45）</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>骑Z3-Z4/跑Z3</t>
         </is>
       </c>
-      <c r="H29" s="15" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>骑行HR要比上周高，感受比赛强度</t>
         </is>
@@ -1725,7 +1737,7 @@
         <is>
           <t>W5 训练高峰
 2026-04-20～2026-04-26
-📌 全周训练量最高峰，骑行最长距离40km，游泳超距1000m，跑步双刺激</t>
+📌 全周训练量最高峰，骑行40km，游泳超距1000m，跑步节奏跑+阈值双刺激</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1750,7 +1762,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>长跑 8km（全程Z2，稳定配速7:00-7:30）</t>
+          <t>长跑 8km（Z2，稳定7:00-7:30配速）</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -1760,7 +1772,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>最长跑，配速不重要，完成为主</t>
+          <t>有氧基础长跑，不追配速</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1810,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>目标&lt;31min，建立信心</t>
+          <t>目标&lt;31min，建立750m余量信心</t>
         </is>
       </c>
     </row>
@@ -1826,15 +1838,19 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>节奏跑：5km（含3km @ Z3-Z4，配速6:10-6:30）</t>
+          <t>阈值间歇：5×1km @Z4，组间90s</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Z3-Z4</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>Z4</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>高峰周最强跑步，配速5:35-6:00</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="6" t="n"/>
@@ -1870,7 +1886,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>高峰周后充分恢复</t>
+          <t>高峰周中段充分恢复</t>
         </is>
       </c>
     </row>
@@ -1898,51 +1914,51 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 5km</t>
+          <t>节奏跑 5km（热身1km+节奏3km @Z3+放松1km）</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Z2</t>
+          <t>Z2-Z3</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="6" t="n"/>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>04/25</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>🚴 BIKE</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>周末全天</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>骑行 40km（Z2-Z3，HR 130-148）</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>骑行 40km（含25km @ Z3，HR 130-148）</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>Z2-Z3</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>全程最长骑行，后半段保持节奏</t>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>全程最长骑行，后半段维持节奏</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1986,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>750m计时+200m放松</t>
+          <t>🎯750m计时（对比W4成绩）</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -1980,7 +1996,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>对比W4成绩，应有进步</t>
+          <t>记录成绩，应有进步</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2005,7 @@
         <is>
           <t>W6 首次全程模拟
 2026-04-27～2026-05-03
-📌 首次完整三项模拟，练习换项（T1/T2），感受比赛流程</t>
+📌 首次完整三项模拟，练习换项（T1/T2），跑步继续保持节奏跑/阈值强度</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -2014,15 +2030,19 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 5km</t>
+          <t>节奏跑 6km（热身1km+节奏4km @6:00-6:20+放松1km）</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr"/>
+          <t>Z3</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>配速比W5再提</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="6" t="n"/>
@@ -2048,17 +2068,17 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>游泳→换项演练：500m游+出水换装计时</t>
+          <t>游泳换项演练：750m游完→出水换装计时</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Z2-Z3</t>
+          <t>Z3</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>练习出水→换装流程，T1目标&lt;2min</t>
+          <t>T1目标&lt;2min，反复练出水动作</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2106,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>节奏跑 5km（含3km @ Z3）</t>
+          <t>阈值间歇：4×1km @Z4，组间90s</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Z2-Z3</t>
+          <t>Z4</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr"/>
@@ -2154,7 +2174,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 4km</t>
+          <t>轻松跑 4km（Z2，为周末模拟保存体能）</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2162,94 +2182,90 @@
           <t>Z2</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>放松为主，为周末模拟保存体能</t>
-        </is>
-      </c>
+      <c r="H42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="6" t="n"/>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>05/02</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>🧱 BRICK</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>周末全天</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>🏁首次完整模拟：游500m→T1换项→骑20km→T2→跑3km</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>🏁首次完整模拟：游750m→T1→骑20km→T2→跑5km</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>比赛强度Z3</t>
         </is>
       </c>
-      <c r="H43" s="15" t="inlineStr">
-        <is>
-          <t>记录各段时间！感受全程节奏</t>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>全程计时！记录各段，感受节奏</t>
         </is>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="13" t="n"/>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>05/03</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>🚴 BIKE</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
         <is>
           <t>周末全天</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>轻松骑 20km 恢复骑</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>轻松骑 20km（主动恢复）</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>Z2</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>昨日模拟后主动恢复</t>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>昨日全程模拟后恢复</t>
         </is>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>W7 完整距离演练
+          <t>W7 强化完整模拟
 2026-05-04～2026-05-10
-📌 完整比赛距离模拟（750m+20km+5km），稳定换项，跑步配速目标6:30</t>
+📌 完整比赛距离第二次模拟，跑步配速目标6:30，骑行提速至26-27km/h</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -2274,12 +2290,12 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 5km</t>
+          <t>节奏跑 7km（热身1km+节奏5km @5:55-6:15+放松1km）</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Z2</t>
+          <t>Z3</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr"/>
@@ -2308,17 +2324,17 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>750m计时+换项演练</t>
+          <t>🎯750m计时+换项演练（对比W6）</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Z3</t>
+          <t>Z3-Z4</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>专注出水→换装速度</t>
+          <t>记录成绩，应有进步</t>
         </is>
       </c>
     </row>
@@ -2346,15 +2362,19 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>砖训后跑：骑跑Brick（骑20km→跑5km @ 6:30-7:00）</t>
+          <t>阈值间歇：5×1km @Z4，组间90s</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>骑Z3/跑Z3</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>Z4</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>配速5:35-6:00/km</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="6" t="n"/>
@@ -2414,7 +2434,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 4km</t>
+          <t>轻松跑 4km（Z2，为周末模拟保存体能）</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -2426,39 +2446,39 @@
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="6" t="n"/>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>05/09</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>🧱 BRICK</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>周末全天</t>
         </is>
       </c>
-      <c r="F50" s="15" t="inlineStr">
-        <is>
-          <t>🏁完整比赛距离：游750m→T1→骑20km→T2→跑5km</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>比赛强度Z3</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="inlineStr">
-        <is>
-          <t>全程计时！目标&lt;2h，记录各段</t>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>🏁完整模拟②：游750m→T1→骑20km（提速26+km/h）→T2→跑5km（目标6:30）</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>比赛强度Z3-Z4</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>对比W6全程时间，应有进步</t>
         </is>
       </c>
     </row>
@@ -2494,18 +2514,14 @@
           <t>Z1-Z2</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>轻松恢复</t>
-        </is>
-      </c>
+      <c r="H51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
           <t>W8 减量一（-30%）
 2026-05-11～2026-05-17
-📌 开始减量，训练量减30%，保持强度感觉，让身体超量恢复</t>
+📌 开始减量，训练量-30%，保持强度感觉不消失，让身体超量恢复</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -2530,15 +2546,19 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 4km</t>
+          <t>节奏跑 5km（热身1km+节奏3km @Z3+放松1km）</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr"/>
+          <t>Z2-Z3</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>缩短距离，保持强度</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="6" t="n"/>
@@ -2564,7 +2584,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>600m轻松游（Z2，感受水感）</t>
+          <t>600m（Z2，感受水感）</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -2598,17 +2618,17 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>节奏跑 4km（含2km @ Z3）</t>
+          <t>阈值间歇：3×1km @Z4，组间90s</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Z2-Z3</t>
+          <t>Z4</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>保持强度感觉，缩短距离</t>
+          <t>组数减少，强度不降</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2690,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 3km</t>
+          <t>轻松跑 4km</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -2682,41 +2702,37 @@
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="6" t="n"/>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="C57" s="11" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>05/16</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>🚴 BIKE</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr">
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t>周末全天</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>轻松骑 20km（Z2，HR&lt;135）</t>
-        </is>
-      </c>
-      <c r="G57" s="11" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="inlineStr">
-        <is>
-          <t>不追速度，享受骑行</t>
-        </is>
-      </c>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>骑行 25km（Z2-Z3，轻松强度）</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>Z2-Z3</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="inlineStr"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="13" t="n"/>
@@ -2757,7 +2773,7 @@
         <is>
           <t>W9 减量二（-50%）
 2026-05-18～2026-05-24
-📌 训练量减50%，赛前最后一次各项计时测试，确认状态</t>
+📌 训练量-50%，赛前最后测试确认状态，保持肌肉激活</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -2782,12 +2798,12 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 3km</t>
+          <t>轻松跑 3km + 4×200m提速跑</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Z2</t>
+          <t>Z2+Z3</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr"/>
@@ -2816,7 +2832,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>🎯赛前游泳测试：750m计时</t>
+          <t>🎯赛前750m计时测试</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -2826,7 +2842,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>对比W5/W7成绩，确认进步</t>
+          <t>对比各周成绩，确认进步</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2938,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>🎯赛前跑步测试：5km配速跑</t>
+          <t>🎯赛前5km配速跑（目标&lt;33min）</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -2930,49 +2946,41 @@
           <t>Z3</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>目标配速6:30/km</t>
-        </is>
-      </c>
+      <c r="H63" s="5" t="inlineStr"/>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="6" t="n"/>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>05/23</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>🚴 BIKE</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="E64" s="14" t="inlineStr">
         <is>
           <t>周末全天</t>
         </is>
       </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>🎯赛前骑行测试：20km计时</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>🎯赛前20km骑行计时（目标&lt;46min）</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>Z3</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
-        <is>
-          <t>目标&lt;48min（25km/h均速）</t>
-        </is>
-      </c>
+      <c r="H64" s="15" t="inlineStr"/>
     </row>
     <row r="65" ht="32" customHeight="1">
       <c r="A65" s="13" t="n"/>
@@ -2998,7 +3006,7 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>休息+装备准备</t>
+          <t>休息+装备最终确认</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -3008,7 +3016,7 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>检查装备，熟悉赛道信息</t>
+          <t>检查装备，熟悉赛道</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3025,7 @@
         <is>
           <t>W10 赛前激活
 2026-05-25～2026-05-30
-📌 极轻量训练保持腿感，比赛前2天完全休息，5/30比赛日</t>
+📌 极轻量训练保腿感，5/28-29完全休息，5/30比赛日全力以赴</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -3042,7 +3050,7 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>轻松游 300m（保感觉）</t>
+          <t>轻松游 300m + 4×50m感受配速</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3076,7 +3084,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>轻松跑 2km + 4×100m提速</t>
+          <t>轻松跑 2km + 6×100m提速跑</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3084,43 +3092,47 @@
           <t>Z1-Z2</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>激活腿部肌肉</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="6" t="n"/>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>05/27</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D68" s="14" t="inlineStr">
         <is>
           <t>🚴 BIKE</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr">
+      <c r="E68" s="14" t="inlineStr">
         <is>
           <t>早7:30-9:00</t>
         </is>
       </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>轻松骑 20min（调整状态）</t>
-        </is>
-      </c>
-      <c r="G68" s="11" t="inlineStr">
+      <c r="F68" s="15" t="inlineStr">
+        <is>
+          <t>轻松骑 20min + 3×1min提速</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
         <is>
           <t>Z1-Z2</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr">
-        <is>
-          <t>检查装备</t>
+      <c r="H68" s="15" t="inlineStr">
+        <is>
+          <t>检查装备，确认变速正常</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3198,7 @@
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>完全休息，装备最终确认</t>
+          <t>完全休息，装备打包</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -3196,7 +3208,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>补充碳水，不要尝试新食物</t>
+          <t>补充碳水，不尝试新食物</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3236,7 @@
       </c>
       <c r="F71" s="18" t="inlineStr">
         <is>
-          <t>🏁 RACE DAY！Sprint铁三 750m+20km+5km</t>
+          <t>🏁 RACE DAY！750m游+20km骑+5km跑</t>
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr">
@@ -3234,7 +3246,7 @@
       </c>
       <c r="H71" s="18" t="inlineStr">
         <is>
-          <t>目标：2小时内完赛！享受过程！</t>
+          <t>目标：2小时内完赛！享受每一刻！</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3332,7 @@
           <t>结构化组次，划水节奏重建</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>25km有氧骑，踏频85rpm</t>
         </is>
@@ -3347,7 +3359,7 @@
           <t>4×200m，换气节奏；600m基准测试</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>30km骑，引入砖训（骑后跑3km）</t>
         </is>
@@ -3374,7 +3386,7 @@
           <t>超距800m，2×400m强度组</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>35km，含15km Z3区间段</t>
         </is>
@@ -3401,7 +3413,7 @@
           <t>🎯750m基准计时测试</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>砖训强度骑（HR 143-155）</t>
         </is>
@@ -3428,7 +3440,7 @@
           <t>超距1000m + 750m计时</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>最长骑行40km</t>
         </is>
@@ -3455,7 +3467,7 @@
           <t>换项演练，游后出水换装</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>首次完整三项模拟（游500+骑20+跑3）</t>
         </is>
@@ -3482,7 +3494,7 @@
           <t>750m计时+换项</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>完整距离：游750+骑20+跑5</t>
         </is>
@@ -3509,7 +3521,7 @@
           <t>600m轻松游，保感觉</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>20km轻骑（Z2）</t>
         </is>
@@ -3536,7 +3548,7 @@
           <t>🎯750m赛前计时</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>🎯20km赛前计时</t>
         </is>
@@ -3563,7 +3575,7 @@
           <t>300m保感觉（5/28停）</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>20min轻骑（5/28停）</t>
         </is>
